--- a/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
+++ b/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6721FB-BEAE-4C79-AB43-726EE7E843B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153D6F27-3B37-4C8C-8E63-3C7EAFFC0F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitHead" sheetId="1" r:id="rId1"/>
@@ -826,7 +826,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -835,8 +835,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -851,6 +858,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -891,18 +903,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -919,9 +934,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -959,9 +974,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -994,9 +1009,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1029,9 +1061,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1206,60 +1255,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BB82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="9" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="40" max="41" width="7" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="9" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="9" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1423,7 +1472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1585,7 +1634,7 @@
       </c>
       <c r="BB2" s="3"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>57</v>
       </c>
@@ -1748,7 +1797,7 @@
       </c>
       <c r="BB3" s="3"/>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>60</v>
       </c>
@@ -1911,7 +1960,7 @@
       </c>
       <c r="BB4" s="3"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>61</v>
       </c>
@@ -2074,7 +2123,7 @@
       </c>
       <c r="BB5" s="3"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>62</v>
       </c>
@@ -2237,7 +2286,7 @@
       </c>
       <c r="BB6" s="3"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>63</v>
       </c>
@@ -2400,7 +2449,7 @@
       </c>
       <c r="BB7" s="3"/>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>64</v>
       </c>
@@ -2563,7 +2612,7 @@
       </c>
       <c r="BB8" s="3"/>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>65</v>
       </c>
@@ -2726,7 +2775,7 @@
       </c>
       <c r="BB9" s="3"/>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>66</v>
       </c>
@@ -2889,7 +2938,7 @@
       </c>
       <c r="BB10" s="3"/>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>68</v>
       </c>
@@ -3052,7 +3101,7 @@
       </c>
       <c r="BB11" s="3"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>70</v>
       </c>
@@ -3215,7 +3264,7 @@
       </c>
       <c r="BB12" s="3"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>72</v>
       </c>
@@ -3378,7 +3427,7 @@
       </c>
       <c r="BB13" s="3"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>73</v>
       </c>
@@ -3541,7 +3590,7 @@
       </c>
       <c r="BB14" s="3"/>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>74</v>
       </c>
@@ -3575,8 +3624,8 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="4">
-        <v>50</v>
+      <c r="L15" s="6">
+        <v>51</v>
       </c>
       <c r="M15" s="4">
         <v>-1</v>
@@ -3704,7 +3753,7 @@
       </c>
       <c r="BB15" s="3"/>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>76</v>
       </c>
@@ -3738,8 +3787,8 @@
       <c r="K16" s="3">
         <v>0</v>
       </c>
-      <c r="L16" s="4">
-        <v>50</v>
+      <c r="L16" s="6">
+        <v>51</v>
       </c>
       <c r="M16" s="4">
         <v>-1</v>
@@ -3867,7 +3916,7 @@
       </c>
       <c r="BB16" s="3"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>77</v>
       </c>
@@ -3901,8 +3950,8 @@
       <c r="K17" s="3">
         <v>0</v>
       </c>
-      <c r="L17" s="4">
-        <v>50</v>
+      <c r="L17" s="6">
+        <v>51</v>
       </c>
       <c r="M17" s="4">
         <v>-1</v>
@@ -4030,7 +4079,7 @@
       </c>
       <c r="BB17" s="3"/>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>78</v>
       </c>
@@ -4193,7 +4242,7 @@
       </c>
       <c r="BB18" s="3"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>80</v>
       </c>
@@ -4356,7 +4405,7 @@
       </c>
       <c r="BB19" s="3"/>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>81</v>
       </c>
@@ -4519,7 +4568,7 @@
       </c>
       <c r="BB20" s="3"/>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>82</v>
       </c>
@@ -4682,7 +4731,7 @@
       </c>
       <c r="BB21" s="3"/>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>84</v>
       </c>
@@ -4845,7 +4894,7 @@
       </c>
       <c r="BB22" s="3"/>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>85</v>
       </c>
@@ -5008,7 +5057,7 @@
       </c>
       <c r="BB23" s="3"/>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>88</v>
       </c>
@@ -5171,7 +5220,7 @@
       </c>
       <c r="BB24" s="3"/>
     </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>89</v>
       </c>
@@ -5334,7 +5383,7 @@
       </c>
       <c r="BB25" s="3"/>
     </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>90</v>
       </c>
@@ -5497,7 +5546,7 @@
       </c>
       <c r="BB26" s="3"/>
     </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>91</v>
       </c>
@@ -5660,7 +5709,7 @@
       </c>
       <c r="BB27" s="3"/>
     </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>92</v>
       </c>
@@ -5823,7 +5872,7 @@
       </c>
       <c r="BB28" s="3"/>
     </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>93</v>
       </c>
@@ -5986,7 +6035,7 @@
       </c>
       <c r="BB29" s="3"/>
     </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>94</v>
       </c>
@@ -6149,7 +6198,7 @@
       </c>
       <c r="BB30" s="3"/>
     </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>96</v>
       </c>
@@ -6312,7 +6361,7 @@
       </c>
       <c r="BB31" s="3"/>
     </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>98</v>
       </c>
@@ -6475,7 +6524,7 @@
       </c>
       <c r="BB32" s="3"/>
     </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>100</v>
       </c>
@@ -6638,7 +6687,7 @@
       </c>
       <c r="BB33" s="3"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>101</v>
       </c>
@@ -6801,7 +6850,7 @@
       </c>
       <c r="BB34" s="3"/>
     </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>102</v>
       </c>
@@ -6835,8 +6884,8 @@
       <c r="K35" s="3">
         <v>0</v>
       </c>
-      <c r="L35" s="4">
-        <v>50</v>
+      <c r="L35" s="6">
+        <v>51</v>
       </c>
       <c r="M35" s="4">
         <v>-1</v>
@@ -6964,7 +7013,7 @@
       </c>
       <c r="BB35" s="3"/>
     </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>104</v>
       </c>
@@ -6998,8 +7047,8 @@
       <c r="K36" s="3">
         <v>0</v>
       </c>
-      <c r="L36" s="4">
-        <v>50</v>
+      <c r="L36" s="6">
+        <v>51</v>
       </c>
       <c r="M36" s="4">
         <v>-1</v>
@@ -7127,7 +7176,7 @@
       </c>
       <c r="BB36" s="3"/>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>105</v>
       </c>
@@ -7161,8 +7210,8 @@
       <c r="K37" s="3">
         <v>0</v>
       </c>
-      <c r="L37" s="4">
-        <v>50</v>
+      <c r="L37" s="6">
+        <v>51</v>
       </c>
       <c r="M37" s="4">
         <v>-1</v>
@@ -7290,7 +7339,7 @@
       </c>
       <c r="BB37" s="3"/>
     </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>106</v>
       </c>
@@ -7453,7 +7502,7 @@
       </c>
       <c r="BB38" s="3"/>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>108</v>
       </c>
@@ -7616,7 +7665,7 @@
       </c>
       <c r="BB39" s="3"/>
     </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>109</v>
       </c>
@@ -7779,7 +7828,7 @@
       </c>
       <c r="BB40" s="3"/>
     </row>
-    <row r="41" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>110</v>
       </c>
@@ -7942,7 +7991,7 @@
       </c>
       <c r="BB41" s="3"/>
     </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>112</v>
       </c>
@@ -8105,7 +8154,7 @@
       </c>
       <c r="BB42" s="3"/>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>113</v>
       </c>
@@ -8268,7 +8317,7 @@
       </c>
       <c r="BB43" s="3"/>
     </row>
-    <row r="44" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>116</v>
       </c>
@@ -8431,7 +8480,7 @@
       </c>
       <c r="BB44" s="3"/>
     </row>
-    <row r="45" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>118</v>
       </c>
@@ -8594,7 +8643,7 @@
       </c>
       <c r="BB45" s="3"/>
     </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>120</v>
       </c>
@@ -8757,7 +8806,7 @@
       </c>
       <c r="BB46" s="3"/>
     </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>122</v>
       </c>
@@ -8920,7 +8969,7 @@
       </c>
       <c r="BB47" s="3"/>
     </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>124</v>
       </c>
@@ -9083,7 +9132,7 @@
       </c>
       <c r="BB48" s="3"/>
     </row>
-    <row r="49" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>126</v>
       </c>
@@ -9246,7 +9295,7 @@
       </c>
       <c r="BB49" s="3"/>
     </row>
-    <row r="50" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>128</v>
       </c>
@@ -9409,7 +9458,7 @@
       </c>
       <c r="BB50" s="3"/>
     </row>
-    <row r="51" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>130</v>
       </c>
@@ -9572,7 +9621,7 @@
       </c>
       <c r="BB51" s="3"/>
     </row>
-    <row r="52" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>132</v>
       </c>
@@ -9735,7 +9784,7 @@
       </c>
       <c r="BB52" s="3"/>
     </row>
-    <row r="53" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>134</v>
       </c>
@@ -9898,7 +9947,7 @@
       </c>
       <c r="BB53" s="3"/>
     </row>
-    <row r="54" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>136</v>
       </c>
@@ -10061,7 +10110,7 @@
       </c>
       <c r="BB54" s="3"/>
     </row>
-    <row r="55" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>138</v>
       </c>
@@ -10224,7 +10273,7 @@
       </c>
       <c r="BB55" s="3"/>
     </row>
-    <row r="56" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>140</v>
       </c>
@@ -10387,7 +10436,7 @@
       </c>
       <c r="BB56" s="3"/>
     </row>
-    <row r="57" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>142</v>
       </c>
@@ -10550,7 +10599,7 @@
       </c>
       <c r="BB57" s="3"/>
     </row>
-    <row r="58" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>144</v>
       </c>
@@ -10713,7 +10762,7 @@
       </c>
       <c r="BB58" s="3"/>
     </row>
-    <row r="59" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>146</v>
       </c>
@@ -10876,7 +10925,7 @@
       </c>
       <c r="BB59" s="3"/>
     </row>
-    <row r="60" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>148</v>
       </c>
@@ -11039,7 +11088,7 @@
       </c>
       <c r="BB60" s="3"/>
     </row>
-    <row r="61" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>150</v>
       </c>
@@ -11202,7 +11251,7 @@
       </c>
       <c r="BB61" s="3"/>
     </row>
-    <row r="62" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>152</v>
       </c>
@@ -11365,7 +11414,7 @@
       </c>
       <c r="BB62" s="3"/>
     </row>
-    <row r="63" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>154</v>
       </c>
@@ -11528,7 +11577,7 @@
       </c>
       <c r="BB63" s="3"/>
     </row>
-    <row r="64" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>157</v>
       </c>
@@ -11691,7 +11740,7 @@
       </c>
       <c r="BB64" s="3"/>
     </row>
-    <row r="65" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>159</v>
       </c>
@@ -11854,7 +11903,7 @@
       </c>
       <c r="BB65" s="3"/>
     </row>
-    <row r="66" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>161</v>
       </c>
@@ -12017,7 +12066,7 @@
       </c>
       <c r="BB66" s="3"/>
     </row>
-    <row r="67" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>163</v>
       </c>
@@ -12180,7 +12229,7 @@
       </c>
       <c r="BB67" s="3"/>
     </row>
-    <row r="68" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>165</v>
       </c>
@@ -12343,7 +12392,7 @@
       </c>
       <c r="BB68" s="3"/>
     </row>
-    <row r="69" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>167</v>
       </c>
@@ -12506,7 +12555,7 @@
       </c>
       <c r="BB69" s="3"/>
     </row>
-    <row r="70" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>169</v>
       </c>
@@ -12669,7 +12718,7 @@
       </c>
       <c r="BB70" s="3"/>
     </row>
-    <row r="71" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>171</v>
       </c>
@@ -12832,7 +12881,7 @@
       </c>
       <c r="BB71" s="3"/>
     </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>173</v>
       </c>
@@ -12995,7 +13044,7 @@
       </c>
       <c r="BB72" s="3"/>
     </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>175</v>
       </c>
@@ -13158,7 +13207,7 @@
       </c>
       <c r="BB73" s="3"/>
     </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>177</v>
       </c>
@@ -13321,7 +13370,7 @@
       </c>
       <c r="BB74" s="3"/>
     </row>
-    <row r="75" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>179</v>
       </c>
@@ -13484,7 +13533,7 @@
       </c>
       <c r="BB75" s="3"/>
     </row>
-    <row r="76" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>181</v>
       </c>
@@ -13647,7 +13696,7 @@
       </c>
       <c r="BB76" s="3"/>
     </row>
-    <row r="77" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>183</v>
       </c>
@@ -13810,7 +13859,7 @@
       </c>
       <c r="BB77" s="3"/>
     </row>
-    <row r="78" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>185</v>
       </c>
@@ -13973,7 +14022,7 @@
       </c>
       <c r="BB78" s="3"/>
     </row>
-    <row r="79" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>187</v>
       </c>
@@ -14136,7 +14185,7 @@
       </c>
       <c r="BB79" s="3"/>
     </row>
-    <row r="80" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>189</v>
       </c>
@@ -14299,7 +14348,7 @@
       </c>
       <c r="BB80" s="3"/>
     </row>
-    <row r="81" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>191</v>
       </c>
@@ -14462,7 +14511,7 @@
       </c>
       <c r="BB81" s="3"/>
     </row>
-    <row r="82" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>193</v>
       </c>
@@ -14634,53 +14683,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AZ82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="6" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>195</v>
       </c>
@@ -14838,7 +14887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>UnitHead!A2</f>
         <v>Code</v>
@@ -15018,7 +15067,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>UnitHead!A3</f>
         <v>unhe001</v>
@@ -15194,7 +15243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>UnitHead!A4</f>
         <v>unhe002</v>
@@ -15370,7 +15419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>UnitHead!A5</f>
         <v>unhe003</v>
@@ -15546,7 +15595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>UnitHead!A6</f>
         <v>unhe004</v>
@@ -15722,7 +15771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>UnitHead!A7</f>
         <v>unhe005</v>
@@ -15898,7 +15947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>UnitHead!A8</f>
         <v>unhe006</v>
@@ -16074,7 +16123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>UnitHead!A9</f>
         <v>unhe007</v>
@@ -16250,7 +16299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>UnitHead!A10</f>
         <v>unhe008</v>
@@ -16426,7 +16475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>UnitHead!A11</f>
         <v>unhe009</v>
@@ -16602,7 +16651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>UnitHead!A12</f>
         <v>unhe010</v>
@@ -16778,7 +16827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>UnitHead!A13</f>
         <v>unhe011</v>
@@ -16954,7 +17003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>UnitHead!A14</f>
         <v>unhe012</v>
@@ -17130,7 +17179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>UnitHead!A15</f>
         <v>unhe013</v>
@@ -17266,7 +17315,7 @@
       </c>
       <c r="AO15">
         <f>UnitHead!L15</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP15">
         <f>UnitHead!N15</f>
@@ -17306,7 +17355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>UnitHead!A16</f>
         <v>unhe014</v>
@@ -17442,7 +17491,7 @@
       </c>
       <c r="AO16">
         <f>UnitHead!L16</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP16">
         <f>UnitHead!N16</f>
@@ -17482,7 +17531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>UnitHead!A17</f>
         <v>unhe015</v>
@@ -17618,7 +17667,7 @@
       </c>
       <c r="AO17">
         <f>UnitHead!L17</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP17">
         <f>UnitHead!N17</f>
@@ -17658,7 +17707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>UnitHead!A18</f>
         <v>unhe016</v>
@@ -17834,7 +17883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>UnitHead!A19</f>
         <v>unhe017</v>
@@ -18010,7 +18059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>UnitHead!A20</f>
         <v>unhe018</v>
@@ -18186,7 +18235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>UnitHead!A21</f>
         <v>unhe019</v>
@@ -18362,7 +18411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>UnitHead!A22</f>
         <v>unhe020</v>
@@ -18538,7 +18587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>UnitHead!A23</f>
         <v>unhe021</v>
@@ -18714,7 +18763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>UnitHead!A24</f>
         <v>unhe022</v>
@@ -18890,7 +18939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>UnitHead!A25</f>
         <v>unhe023</v>
@@ -19066,7 +19115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>UnitHead!A26</f>
         <v>unhe024</v>
@@ -19242,7 +19291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>UnitHead!A27</f>
         <v>unhe025</v>
@@ -19418,7 +19467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>UnitHead!A28</f>
         <v>unhe026</v>
@@ -19594,7 +19643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>UnitHead!A29</f>
         <v>unhe027</v>
@@ -19770,7 +19819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>UnitHead!A30</f>
         <v>unhe028</v>
@@ -19946,7 +19995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>UnitHead!A31</f>
         <v>unhe029</v>
@@ -20122,7 +20171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>UnitHead!A32</f>
         <v>unhe030</v>
@@ -20298,7 +20347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>UnitHead!A33</f>
         <v>unhe031</v>
@@ -20474,7 +20523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>UnitHead!A34</f>
         <v>unhe032</v>
@@ -20650,7 +20699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>UnitHead!A35</f>
         <v>unhe033</v>
@@ -20786,7 +20835,7 @@
       </c>
       <c r="AO35">
         <f>UnitHead!L35</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP35">
         <f>UnitHead!N35</f>
@@ -20826,7 +20875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>UnitHead!A36</f>
         <v>unhe034</v>
@@ -20962,7 +21011,7 @@
       </c>
       <c r="AO36">
         <f>UnitHead!L36</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP36">
         <f>UnitHead!N36</f>
@@ -21002,7 +21051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>UnitHead!A37</f>
         <v>unhe035</v>
@@ -21138,7 +21187,7 @@
       </c>
       <c r="AO37">
         <f>UnitHead!L37</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP37">
         <f>UnitHead!N37</f>
@@ -21178,7 +21227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>UnitHead!A38</f>
         <v>unhe036</v>
@@ -21354,7 +21403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>UnitHead!A39</f>
         <v>unhe037</v>
@@ -21530,7 +21579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>UnitHead!A40</f>
         <v>unhe038</v>
@@ -21706,7 +21755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>UnitHead!A41</f>
         <v>unhe039</v>
@@ -21882,7 +21931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>UnitHead!A42</f>
         <v>unhe040</v>
@@ -22058,7 +22107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>UnitHead!A43</f>
         <v>unhe041</v>
@@ -22234,7 +22283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>UnitHead!A44</f>
         <v>unhe042</v>
@@ -22410,7 +22459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>UnitHead!A45</f>
         <v>unhe043</v>
@@ -22586,7 +22635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>UnitHead!A46</f>
         <v>unhe044</v>
@@ -22762,7 +22811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>UnitHead!A47</f>
         <v>unhe045</v>
@@ -22938,7 +22987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>UnitHead!A48</f>
         <v>unhe046</v>
@@ -23114,7 +23163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>UnitHead!A49</f>
         <v>unhe047</v>
@@ -23290,7 +23339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>UnitHead!A50</f>
         <v>unhe048</v>
@@ -23466,7 +23515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>UnitHead!A51</f>
         <v>unhe049</v>
@@ -23642,7 +23691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>UnitHead!A52</f>
         <v>unhe050</v>
@@ -23818,7 +23867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>UnitHead!A53</f>
         <v>unhe051</v>
@@ -23994,7 +24043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>UnitHead!A54</f>
         <v>unhe052</v>
@@ -24170,7 +24219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>UnitHead!A55</f>
         <v>unhe053</v>
@@ -24346,7 +24395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>UnitHead!A56</f>
         <v>unhe054</v>
@@ -24522,7 +24571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>UnitHead!A57</f>
         <v>unhe055</v>
@@ -24698,7 +24747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>UnitHead!A58</f>
         <v>unhe056</v>
@@ -24874,7 +24923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f>UnitHead!A59</f>
         <v>unhe057</v>
@@ -25050,7 +25099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f>UnitHead!A60</f>
         <v>unhe058</v>
@@ -25226,7 +25275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f>UnitHead!A61</f>
         <v>unhe059</v>
@@ -25402,7 +25451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f>UnitHead!A62</f>
         <v>unhe060</v>
@@ -25578,7 +25627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f>UnitHead!A63</f>
         <v>unhe061</v>
@@ -25754,7 +25803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f>UnitHead!A64</f>
         <v>unhe062</v>
@@ -25930,7 +25979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f>UnitHead!A65</f>
         <v>unhe063</v>
@@ -26106,7 +26155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f>UnitHead!A66</f>
         <v>unhe064</v>
@@ -26282,7 +26331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f>UnitHead!A67</f>
         <v>unhe065</v>
@@ -26458,7 +26507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>UnitHead!A68</f>
         <v>unhe066</v>
@@ -26634,7 +26683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f>UnitHead!A69</f>
         <v>unhe067</v>
@@ -26810,7 +26859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f>UnitHead!A70</f>
         <v>unhe068</v>
@@ -26986,7 +27035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f>UnitHead!A71</f>
         <v>unhe069</v>
@@ -27162,7 +27211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f>UnitHead!A72</f>
         <v>unhe070</v>
@@ -27338,7 +27387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f>UnitHead!A73</f>
         <v>unhe071</v>
@@ -27514,7 +27563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f>UnitHead!A74</f>
         <v>unhe072</v>
@@ -27690,7 +27739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f>UnitHead!A75</f>
         <v>unhe073</v>
@@ -27866,7 +27915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f>UnitHead!A76</f>
         <v>unhe074</v>
@@ -28042,7 +28091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f>UnitHead!A77</f>
         <v>unhe075</v>
@@ -28218,7 +28267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f>UnitHead!A78</f>
         <v>unhe076</v>
@@ -28394,7 +28443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f>UnitHead!A79</f>
         <v>unhe077</v>
@@ -28570,7 +28619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f>UnitHead!A80</f>
         <v>unhe078</v>
@@ -28746,7 +28795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f>UnitHead!A81</f>
         <v>unhe079</v>
@@ -28922,7 +28971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f>UnitHead!A82</f>
         <v>unhe080</v>
@@ -29107,9 +29156,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -29120,7 +29169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>200</v>
       </c>
@@ -29129,7 +29178,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>0</v>
       </c>
@@ -29138,7 +29187,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -29147,7 +29196,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -29156,7 +29205,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -29165,7 +29214,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -29174,7 +29223,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -29183,7 +29232,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -29192,7 +29241,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -29201,7 +29250,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -29210,7 +29259,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -29219,7 +29268,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -29228,7 +29277,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -29237,7 +29286,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>12</v>
       </c>
@@ -29246,7 +29295,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>13</v>
       </c>
@@ -29255,7 +29304,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -29264,7 +29313,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -29273,7 +29322,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -29282,7 +29331,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>17</v>
       </c>
@@ -29291,7 +29340,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -29300,7 +29349,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -29309,7 +29358,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -29318,7 +29367,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>21</v>
       </c>
@@ -29327,7 +29376,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>22</v>
       </c>
@@ -29336,7 +29385,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>23</v>
       </c>
@@ -29345,7 +29394,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>24</v>
       </c>
@@ -29354,7 +29403,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>25</v>
       </c>
@@ -29363,7 +29412,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -29372,7 +29421,7 @@
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>27</v>
       </c>
@@ -29381,7 +29430,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>28</v>
       </c>
@@ -29390,7 +29439,7 @@
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>29</v>
       </c>
@@ -29399,7 +29448,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>30</v>
       </c>
@@ -29408,7 +29457,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>31</v>
       </c>
@@ -29417,7 +29466,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>32</v>
       </c>
@@ -29426,7 +29475,7 @@
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>33</v>
       </c>
@@ -29435,7 +29484,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>34</v>
       </c>
@@ -29444,7 +29493,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>35</v>
       </c>
@@ -29453,7 +29502,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>36</v>
       </c>
@@ -29462,7 +29511,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>37</v>
       </c>
@@ -29471,7 +29520,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>38</v>
       </c>
@@ -29480,7 +29529,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>39</v>
       </c>
@@ -29489,7 +29538,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>40</v>
       </c>
@@ -29498,7 +29547,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>41</v>
       </c>
@@ -29507,7 +29556,7 @@
       </c>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>42</v>
       </c>
@@ -29516,7 +29565,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>43</v>
       </c>
@@ -29525,7 +29574,7 @@
       </c>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>44</v>
       </c>
@@ -29534,7 +29583,7 @@
       </c>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>45</v>
       </c>
@@ -29543,7 +29592,7 @@
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>46</v>
       </c>
@@ -29552,7 +29601,7 @@
       </c>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>47</v>
       </c>
@@ -29561,7 +29610,7 @@
       </c>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>48</v>
       </c>
@@ -29570,7 +29619,7 @@
       </c>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>49</v>
       </c>
@@ -29579,7 +29628,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>50</v>
       </c>
@@ -29588,7 +29637,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>51</v>
       </c>
@@ -29597,7 +29646,7 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>52</v>
       </c>
@@ -29606,7 +29655,7 @@
       </c>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>53</v>
       </c>
@@ -29615,7 +29664,7 @@
       </c>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>54</v>
       </c>
@@ -29624,7 +29673,7 @@
       </c>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>55</v>
       </c>
@@ -29633,7 +29682,7 @@
       </c>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>56</v>
       </c>
@@ -29642,7 +29691,7 @@
       </c>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>57</v>
       </c>
@@ -29651,7 +29700,7 @@
       </c>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>58</v>
       </c>
@@ -29660,7 +29709,7 @@
       </c>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>59</v>
       </c>
@@ -29669,7 +29718,7 @@
       </c>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>60</v>
       </c>
@@ -29678,7 +29727,7 @@
       </c>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>61</v>
       </c>
@@ -29687,7 +29736,7 @@
       </c>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>62</v>
       </c>
@@ -29696,7 +29745,7 @@
       </c>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>63</v>
       </c>
@@ -29705,7 +29754,7 @@
       </c>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>64</v>
       </c>
@@ -29714,7 +29763,7 @@
       </c>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>65</v>
       </c>
@@ -29723,7 +29772,7 @@
       </c>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>66</v>
       </c>
@@ -29732,7 +29781,7 @@
       </c>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>67</v>
       </c>
@@ -29741,7 +29790,7 @@
       </c>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>68</v>
       </c>
@@ -29750,7 +29799,7 @@
       </c>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>69</v>
       </c>
@@ -29759,7 +29808,7 @@
       </c>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>70</v>
       </c>
@@ -29768,7 +29817,7 @@
       </c>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>71</v>
       </c>
@@ -29777,7 +29826,7 @@
       </c>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>72</v>
       </c>
@@ -29786,7 +29835,7 @@
       </c>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>73</v>
       </c>
@@ -29795,7 +29844,7 @@
       </c>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>74</v>
       </c>
@@ -29804,7 +29853,7 @@
       </c>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>75</v>
       </c>
@@ -29813,7 +29862,7 @@
       </c>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>76</v>
       </c>
@@ -29822,7 +29871,7 @@
       </c>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>77</v>
       </c>
@@ -29831,7 +29880,7 @@
       </c>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>78</v>
       </c>
@@ -29840,7 +29889,7 @@
       </c>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>79</v>
       </c>

--- a/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
+++ b/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153D6F27-3B37-4C8C-8E63-3C7EAFFC0F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E794F8B-C4A2-4A7D-A1AA-81B44F1A01A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,7 +826,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -842,8 +842,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -863,6 +870,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -903,11 +915,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -915,9 +928,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6687,168 +6704,168 @@
       </c>
       <c r="BB33" s="3"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:54" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="7">
         <v>5</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="E34" s="4">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="s">
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4">
+      <c r="G34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0</v>
+      </c>
+      <c r="K34" s="8">
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
         <v>48</v>
       </c>
-      <c r="M34" s="4">
-        <v>-1</v>
-      </c>
-      <c r="N34" s="4">
-        <v>2</v>
-      </c>
-      <c r="O34" s="4">
+      <c r="M34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="7">
+        <v>2</v>
+      </c>
+      <c r="O34" s="7">
         <v>93</v>
       </c>
-      <c r="P34" s="4">
-        <v>-1</v>
-      </c>
-      <c r="Q34" s="4">
-        <v>-1</v>
-      </c>
-      <c r="R34" s="3">
+      <c r="P34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="Q34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="R34" s="8">
         <v>1</v>
       </c>
-      <c r="S34" s="3">
-        <v>0</v>
-      </c>
-      <c r="T34" s="3">
-        <v>0</v>
-      </c>
-      <c r="U34" s="3">
-        <v>0</v>
-      </c>
-      <c r="V34" s="3">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="X34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Y34" s="3">
+      <c r="S34" s="8">
+        <v>0</v>
+      </c>
+      <c r="T34" s="8">
+        <v>0</v>
+      </c>
+      <c r="U34" s="8">
+        <v>0</v>
+      </c>
+      <c r="V34" s="8">
+        <v>0</v>
+      </c>
+      <c r="W34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="X34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="Y34" s="8">
         <v>247</v>
       </c>
-      <c r="Z34" s="3">
-        <v>50</v>
-      </c>
-      <c r="AA34" s="3">
-        <v>50</v>
-      </c>
-      <c r="AB34" s="4">
-        <v>1325</v>
-      </c>
-      <c r="AC34" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AE34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="4">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="4">
+      <c r="Z34" s="8">
+        <v>50</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>50</v>
+      </c>
+      <c r="AB34" s="7">
+        <v>1025</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>50</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="AE34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="7">
         <v>1900000</v>
       </c>
-      <c r="AK34" s="4">
+      <c r="AK34" s="7">
         <v>1</v>
       </c>
-      <c r="AL34" s="4">
+      <c r="AL34" s="7">
         <v>1</v>
       </c>
-      <c r="AM34" s="3">
+      <c r="AM34" s="8">
         <v>38000</v>
       </c>
-      <c r="AN34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY34" s="3" t="str">
+      <c r="AN34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY34" s="8" t="str">
         <f t="shared" si="0"/>
         <v>tunhe032</v>
       </c>
-      <c r="AZ34" s="4">
-        <v>-1</v>
-      </c>
-      <c r="BA34" s="4">
-        <v>2</v>
-      </c>
-      <c r="BB34" s="3"/>
+      <c r="AZ34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="BA34" s="7">
+        <v>2</v>
+      </c>
+      <c r="BB34" s="8"/>
     </row>
     <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
@@ -20617,7 +20634,7 @@
       </c>
       <c r="AB34">
         <f>UnitHead!AB34</f>
-        <v>1325</v>
+        <v>1025</v>
       </c>
       <c r="AC34" s="5">
         <v>0</v>

--- a/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
+++ b/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E794F8B-C4A2-4A7D-A1AA-81B44F1A01A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C5F2F2-5DC1-48EB-B78C-88CE430AC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="7">
-        <v>1900000</v>
+        <v>90909382</v>
       </c>
       <c r="AK34" s="7">
         <v>1</v>
@@ -20572,7 +20572,7 @@
       </c>
       <c r="I34">
         <f>UnitHead!AJ34</f>
-        <v>1900000</v>
+        <v>90909382</v>
       </c>
       <c r="J34">
         <f>UnitHead!AK34</f>

--- a/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
+++ b/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C5F2F2-5DC1-48EB-B78C-88CE430AC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787A4E2B-1A14-4ADF-8E34-3B75D5768CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitHead" sheetId="1" r:id="rId1"/>
@@ -850,7 +850,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -875,6 +875,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -920,7 +926,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -931,6 +937,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -951,9 +960,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -991,9 +1000,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1026,26 +1035,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1078,26 +1070,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3444,168 +3419,168 @@
       </c>
       <c r="BB13" s="3"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="4">
-        <v>2</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="10">
+        <v>2</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E14" s="10">
+        <v>0</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
+      <c r="G14" s="11">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="11">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
         <v>48</v>
       </c>
-      <c r="M14" s="4">
-        <v>-1</v>
-      </c>
-      <c r="N14" s="4">
-        <v>2</v>
-      </c>
-      <c r="O14" s="4">
+      <c r="M14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="N14" s="10">
+        <v>2</v>
+      </c>
+      <c r="O14" s="10">
         <v>93</v>
       </c>
-      <c r="P14" s="4">
-        <v>-1</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>-1</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="P14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="R14" s="11">
         <v>1</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="X14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="S14" s="11">
+        <v>0</v>
+      </c>
+      <c r="T14" s="11">
+        <v>0</v>
+      </c>
+      <c r="U14" s="11">
+        <v>0</v>
+      </c>
+      <c r="V14" s="11">
+        <v>0</v>
+      </c>
+      <c r="W14" s="11">
+        <v>-1</v>
+      </c>
+      <c r="X14" s="11">
+        <v>-1</v>
+      </c>
+      <c r="Y14" s="11">
         <v>190</v>
       </c>
-      <c r="Z14" s="3">
-        <v>50</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>50</v>
-      </c>
-      <c r="AB14" s="4">
-        <v>2151</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="4">
-        <v>1900000</v>
-      </c>
-      <c r="AK14" s="4">
+      <c r="Z14" s="11">
+        <v>50</v>
+      </c>
+      <c r="AA14" s="11">
+        <v>50</v>
+      </c>
+      <c r="AB14" s="10">
+        <v>1751</v>
+      </c>
+      <c r="AC14" s="11">
+        <v>50</v>
+      </c>
+      <c r="AD14" s="11">
+        <v>-1</v>
+      </c>
+      <c r="AE14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="7">
+        <v>3136363</v>
+      </c>
+      <c r="AK14" s="10">
         <v>1</v>
       </c>
-      <c r="AL14" s="4">
+      <c r="AL14" s="10">
         <v>1</v>
       </c>
-      <c r="AM14" s="3">
-        <v>38000</v>
-      </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY14" s="3" t="str">
+      <c r="AM14" s="7">
+        <v>313636</v>
+      </c>
+      <c r="AN14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="11" t="str">
         <f t="shared" si="0"/>
         <v>tunhe012</v>
       </c>
-      <c r="AZ14" s="4">
-        <v>-1</v>
-      </c>
-      <c r="BA14" s="4">
-        <v>2</v>
-      </c>
-      <c r="BB14" s="3"/>
+      <c r="AZ14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="BA14" s="10">
+        <v>2</v>
+      </c>
+      <c r="BB14" s="11"/>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -6811,7 +6786,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="7">
-        <v>90909382</v>
+        <v>3136363</v>
       </c>
       <c r="AK34" s="7">
         <v>1</v>
@@ -6819,8 +6794,8 @@
       <c r="AL34" s="7">
         <v>1</v>
       </c>
-      <c r="AM34" s="8">
-        <v>38000</v>
+      <c r="AM34" s="7">
+        <v>313636</v>
       </c>
       <c r="AN34" s="8">
         <v>0</v>
@@ -17052,7 +17027,7 @@
       </c>
       <c r="I14">
         <f>UnitHead!AJ14</f>
-        <v>1900000</v>
+        <v>3136363</v>
       </c>
       <c r="J14">
         <f>UnitHead!AK14</f>
@@ -17114,7 +17089,7 @@
       </c>
       <c r="AB14">
         <f>UnitHead!AB14</f>
-        <v>2151</v>
+        <v>1751</v>
       </c>
       <c r="AC14" s="5">
         <v>0</v>
@@ -20572,7 +20547,7 @@
       </c>
       <c r="I34">
         <f>UnitHead!AJ34</f>
-        <v>90909382</v>
+        <v>3136363</v>
       </c>
       <c r="J34">
         <f>UnitHead!AK34</f>

--- a/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
+++ b/gu_in/Item.edf/37_UnitHead/UnitHead.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787A4E2B-1A14-4ADF-8E34-3B75D5768CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2AF9A1-8127-43E2-BAD2-AC4A5286F23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitHead" sheetId="1" r:id="rId1"/>
@@ -960,9 +960,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1000,9 +1000,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1035,9 +1035,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1070,9 +1087,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6786,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="7">
-        <v>3136363</v>
+        <v>6272726</v>
       </c>
       <c r="AK34" s="7">
         <v>1</v>
@@ -6795,7 +6829,7 @@
         <v>1</v>
       </c>
       <c r="AM34" s="7">
-        <v>313636</v>
+        <v>909091</v>
       </c>
       <c r="AN34" s="8">
         <v>0</v>
@@ -20547,7 +20581,7 @@
       </c>
       <c r="I34">
         <f>UnitHead!AJ34</f>
-        <v>3136363</v>
+        <v>6272726</v>
       </c>
       <c r="J34">
         <f>UnitHead!AK34</f>
